--- a/02_加值成品/九下/九下2-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/九下/九下2-1_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三下學期 九下2-1 磁鐵與磁場　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國三下學期 九下2-1 磁鐵與磁場　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>磁鐵有哪兩極？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>互斥難以貼合</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>N極</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>互相排斥</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>南極S北極N</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>兩極</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>同磁極相吸還相斥？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>相吸</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>磁場</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>大磁鐵</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>相斥</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>同極</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>異磁極相吸還相斥？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>越強</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>不會</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>相吸</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>S極</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>異極</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>磁力作用的空間稱？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>磁場</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>不會</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>地球磁場</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>空間</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>磁力線由哪極出發？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>地球磁場</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>磁場</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>相斥</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>N極</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>外部</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>磁力線進入哪極？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>相斥</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>S極</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>地理北方</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>磁力線</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>外部</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>磁力線越密磁場？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>相斥</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>磁場</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>互斥難以貼合</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>越強</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>疏密</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>指南針利用什麼指方向？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>相斥</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>地理北方</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>磁場</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>地球磁場</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>地磁</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>磁鐵磁性最強的部位是？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>兩極</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>地理北方</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>相吸</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>南極S北極N</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>磁極</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>磁鐵的兩極分別是N極與？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>不會</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>相吸</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>S極</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>地球磁場</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>兩極</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三下學期 九下2-1 磁鐵與磁場　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國三下學期 九下2-1 磁鐵與磁場　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>磁鐵切成兩半後？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>地磁極接近但不完全等於地理極</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>越密處磁場越強</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>仍各有N、S極</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>各有N、S兩極</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>不可分</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>磁力線會相交嗎？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>S極</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>不會</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>相斥</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>磁場</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>不交</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>越靠近磁極磁場？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>相吸</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>同極斥異極吸</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>相斥</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>越強</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>強度</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>指南針N極大致指向？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>地理北方</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>互斥難以貼合</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>越強</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>相吸</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>地磁</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>磁極能單獨存在嗎？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>磁力線</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>同極斥異極吸</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>相吸</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>不能</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>成對</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>磁力線疏的地方磁場？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>地球磁場</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>較弱</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>互相排斥</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>磁力線</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>疏</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>兩磁鐵N對N會？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>磁場</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>互相排斥</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>地球磁場</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>同極</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>地球本身像一個？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>相斥</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>大磁鐵</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>不會</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>互相排斥</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>地磁</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>磁力線在磁鐵外部由N到？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>相斥</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>較弱</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>S極</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>方向</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>兩磁鐵異極靠近會？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>相吸</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>S極</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>磁場</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>南極S北極N</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>異極吸</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三下學期 九下2-1 磁鐵與磁場　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國三下學期 九下2-1 磁鐵與磁場　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>為何磁鐵無論怎麼切都有兩極？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>磁性來自內部,無法分出單極</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>某點磁場方向唯一</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>仍各有N、S極</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>地磁極接近但不完全等於地理極</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>本質</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>用磁力線疏密如何判斷磁場強弱？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>各有N、S兩極</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>受地球磁場作用而定向</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>地磁極接近但不完全等於地理極</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>越密處磁場越強</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>讀圖</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>指南針為何能指南北？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>受地球磁場作用而定向</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>磁性來自內部,無法分出單極</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>地磁極接近但不完全等於地理極</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>某點磁場方向唯一</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>地磁</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>兩磁鐵靠近時如何判斷吸引或排斥？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>同極斥異極吸</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>磁場</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>相吸</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>南極S北極N</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>判斷</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>磁力線不相交的意義？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>地磁極接近但不完全等於地理極</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>某點磁場方向唯一</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>仍各有N、S極</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>越密處磁場越強</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>唯一性</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>地磁的N、S與地理南北關係(概念)？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>地磁極接近但不完全等於地理極</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>各有N、S兩極</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>受地球磁場作用而定向</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>磁性來自內部,無法分出單極</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>地磁</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>如何用鐵粉觀察磁場分布？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>仍各有N、S極</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>鐵粉沿磁力線排列顯現</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>某點磁場方向唯一</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>越密處磁場越強</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>實驗</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>把兩塊磁鐵N極相接會如何？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>互斥難以貼合</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>相吸</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>南極S北極N</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>越強</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>同極斥</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>把長條磁鐵折斷成兩段各段有幾極？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>各有N、S兩極</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>地磁極接近但不完全等於地理極</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>受地球磁場作用而定向</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>越密處磁場越強</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>不可分</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>用鐵粉撒在磁鐵上會沿什麼排列？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>磁場</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>相斥</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>磁力線</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>觀察</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/九下/九下2-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/九下/九下2-1_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>兩極</t>
+          <t>兩極：每一個磁鐵都有南極(S)和北極(N)兩個磁極，這是磁鐵的基本性質</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>同極</t>
+          <t>同極：兩個相同的磁極(N對N或S對S)靠近時會互相推開，這叫同極相斥</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>異極</t>
+          <t>異極：一個N極和一個S極靠近時會互相吸引在一起，這叫異極相吸</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>空間</t>
+          <t>空間：磁鐵周圍能感受到磁力作用的整個區域，就稱為磁場</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>外部</t>
+          <t>外部：畫磁力線時，習慣上都是從磁鐵的N極出發，向外延伸出去</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>外部</t>
+          <t>外部：磁力線繞出去後，最後會回到磁鐵的S極，形成一圈完整的線</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>疏密</t>
+          <t>疏密：磁力線畫得越密集的地方，代表那個位置的磁場強度越強</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>地磁</t>
+          <t>地磁：指南針的磁針受到地球本身磁場的作用，才能穩定指向南北方</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>磁極</t>
+          <t>磁極：磁鐵的磁力集中在兩端，也就是N極和S極附近磁性最強</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>兩極</t>
+          <t>兩極：每個磁鐵都同時具有N極和S極這兩個磁極</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>不可分</t>
+          <t>不可分：把一塊磁鐵切成兩半，每一半都會重新出現完整的N極和S極</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>不交</t>
+          <t>不交：磁力線在空間中不會互相交叉，因為每一點的磁場方向只有一個</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>強度</t>
+          <t>強度：離磁鐵的磁極越近，感受到的磁力作用就越強</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>地磁</t>
+          <t>地磁：指南針的N極會大致指向地理上的北方，因為地球本身像個大磁鐵</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>成對</t>
+          <t>成對：磁鐵的N極和S極永遠成對出現，無法把單獨一個磁極分離出來</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>疏</t>
+          <t>疏：磁力線畫得比較稀疏、分散的地方，代表那裡的磁場比較弱</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>同極</t>
+          <t>同極：兩塊磁鐵的N極互相靠近時，因為是同極，所以會互相排斥推開</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>地磁</t>
+          <t>地磁：地球內部產生的磁場效果，就好像地球本身是一個巨大的磁鐵一樣</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>方向</t>
+          <t>方向：磁力線在磁鐵外部的走向習慣定為從N極出發，繞到S極</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>異極吸</t>
+          <t>異極吸：一個N極和一個S極靠近時屬於異極，會互相吸引在一起</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>本質</t>
+          <t>本質：磁鐵的磁性來自內部結構本身，不管切成多小的一塊，每一塊都會重新出現一對磁極</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>讀圖</t>
+          <t>讀圖：觀察磁力線圖時，線條畫得越密集的位置，代表該處的磁場越強；越稀疏則磁場越弱</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>地磁</t>
+          <t>地磁：地球本身像一個大磁鐵，指南針的磁針受到地球磁場作用，會自然轉向南北方向</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>判斷</t>
+          <t>判斷：先看兩邊靠近的磁極是不是一樣，相同的極(同極)會互斥，不同的極(異極)會互相吸引</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>唯一性</t>
+          <t>唯一性：空間中任何一個位置的磁場方向只會有一個，所以代表磁場方向的磁力線不會互相交叉</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>地磁</t>
+          <t>地磁：地球磁場的磁極位置和地理上真正的南北極很接近，但兩者並不完全重疊</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>實驗</t>
+          <t>實驗：把鐵粉均勻灑在磁鐵附近，鐵粉會受磁力影響，自動排列成一條條磁力線的形狀</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>同極斥</t>
+          <t>同極斥：兩塊磁鐵的N極是相同磁極，靠近時會互相推開，很難把它們貼在一起</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>不可分</t>
+          <t>不可分：磁鐵不管切成幾段，每一段都會重新出現完整的N極和S極，無法拆成單一磁極</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>觀察</t>
+          <t>觀察：鐵粉受磁力影響會自動排列成一條條線，顯示出磁力線的分布形狀</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/九下/九下2-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/九下/九下2-1_三種難度測驗卷.xlsx
@@ -563,17 +563,17 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>互斥難以貼合</t>
+          <t>S極</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>N極</t>
+          <t>同極斥異極吸</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>互相排斥</t>
+          <t>磁力線</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -688,17 +688,17 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>不能</t>
+          <t>大磁鐵</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>不會</t>
+          <t>N極</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>地球磁場</t>
+          <t>磁力線</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>相斥</t>
+          <t>N極</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>地理北方</t>
+          <t>相吸</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -843,17 +843,17 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>相斥</t>
+          <t>地理北方</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>地理北方</t>
+          <t>大磁鐵</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>磁場</t>
+          <t>較弱</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -923,12 +923,12 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>不會</t>
+          <t>地球磁場</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>相吸</t>
+          <t>互相排斥</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>地球磁場</t>
+          <t>大磁鐵</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>相斥</t>
+          <t>大磁鐵</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>較弱</t>
+          <t>越強</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>S極</t>
+          <t>兩極</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
